--- a/Level Overview.xlsx
+++ b/Level Overview.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\John\Documents\src\github\ai\kings-messenger\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1FE955CC-9F69-4A8D-AFAF-B45DC5C010F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{611532EA-B585-4AF7-9852-EE5E7D0E7CFB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{4ECBEB57-A43B-48B5-9C6B-4CAA76C8E0E0}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="14">
   <si>
     <t>Level Number</t>
   </si>
@@ -78,6 +78,9 @@
   </si>
   <si>
     <t>Skaldsund</t>
+  </si>
+  <si>
+    <t>Brambeldyke</t>
   </si>
 </sst>
 </file>
@@ -514,6 +517,15 @@
       <c r="B4" t="s">
         <v>5</v>
       </c>
+      <c r="C4" t="s">
+        <v>13</v>
+      </c>
+      <c r="D4">
+        <v>120</v>
+      </c>
+      <c r="E4">
+        <v>30</v>
+      </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A5">

--- a/Level Overview.xlsx
+++ b/Level Overview.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\John\Documents\src\github\ai\kings-messenger\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/e7585a4db9994b00/Documents/src/github/ai/kings-messenger/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{611532EA-B585-4AF7-9852-EE5E7D0E7CFB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="5" documentId="13_ncr:1_{611532EA-B585-4AF7-9852-EE5E7D0E7CFB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{359AF4D3-2C58-4BCF-9924-D0F7B6C79092}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{4ECBEB57-A43B-48B5-9C6B-4CAA76C8E0E0}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="15">
   <si>
     <t>Level Number</t>
   </si>
@@ -81,6 +81,9 @@
   </si>
   <si>
     <t>Brambeldyke</t>
+  </si>
+  <si>
+    <t>Gallowscroft</t>
   </si>
 </sst>
 </file>
@@ -534,6 +537,15 @@
       <c r="B5" t="s">
         <v>6</v>
       </c>
+      <c r="C5" t="s">
+        <v>14</v>
+      </c>
+      <c r="D5">
+        <v>80</v>
+      </c>
+      <c r="E5">
+        <v>42</v>
+      </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A6">

--- a/Level Overview.xlsx
+++ b/Level Overview.xlsx
@@ -16,6 +16,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -136,6 +137,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
